--- a/Assets/_Game/Introduce/基础召唤物/5费英雄.xlsx
+++ b/Assets/_Game/Introduce/基础召唤物/5费英雄.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2fdd5e1cd6b09a2c/Desktop/异界（Another World）/基础召唤物/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="421" documentId="11_AD4DA82427541F7ACA7EB89B78481DA46BE8DE12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4845C11C-74C8-49D0-A7F4-4958A0EE9771}"/>
+  <xr:revisionPtr revIDLastSave="429" documentId="11_AD4DA82427541F7ACA7EB89B78481DA46BE8DE12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15754FDC-7F4C-4C94-84A9-1F39EDCC5EB3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -487,10 +487,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.进场：召唤两名渊：幽魂，基础   2.己方受到的伤害将转为直接扣除领主生命值而代替承担</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.进场：召唤两名机械：杂兵，为己方场上或手牌中一召唤物附加机械前缀   2.每阶段开始若己方存在三名带有机械前缀的召唤物，全体+1+1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -507,15 +503,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.进场：为己方一名召唤物（除了自己）附加祝福，生命值&lt;=0的瞬间立刻回满至上限，同时+2+1，并触发一次进场（目标召唤物离开场内时祝福失效）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.对位攻击后若使攻击或特性作用目标退场，则本次战斗回合自己最多扣1生命值，并恢复玩家1生命值     2.不受对方非反制牌法术影响</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.进场：选择是否复制对方基础召唤费用为1或3的一召唤物的一个进场或抛置，并触发复制的特性，最多复制4个   2.退场：回到手牌    3.己方回合开始退场并+2能量    4.每阶段至多触发进场特性和抛置特性一次，进场时会同时触发该召唤物的抛置特性</t>
+    <t>1.进场：召唤两名渊：幽魂，基础   2.己方召唤物受到的伤害将转为直接扣除领主生命值而代替承担</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.进场：为己方一名召唤物（除了自己）附加祝福，生命值&lt;=0的瞬间立刻回满至上限，同时+3+3（目标召唤物离开场内时祝福失效）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.进场：选择是否复制对方基础召唤费用为1或3的一召唤物的一个进场或抛置，并触发复制的特性，最多复制4个   2.退场：回到手牌    3.己方回合开始退场并+2能量    （该召唤物的每个特性处理完成才进行下个特性）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G4" s="1">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -1134,7 +1134,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1176,7 +1176,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -1218,7 +1218,7 @@
         <v>5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1341,7 +1341,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>122</v>
@@ -1428,7 +1428,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2310,7 +2310,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
